--- a/weekdates.xlsx
+++ b/weekdates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df58896beb6fd7a3/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAC3E\OneDrive\Documents\CursorCodes\OneGMS\snapshots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DCB849A-29B1-4BC6-9EF2-4E8BF45A8683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B008835F-2011-4F19-8A99-CA836F1207E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40680" yWindow="-19110" windowWidth="34905" windowHeight="17055" xr2:uid="{0194F69E-157E-4D67-91A0-CF52279CBF62}"/>
+    <workbookView xWindow="41115" yWindow="-19335" windowWidth="24915" windowHeight="17715" xr2:uid="{0194F69E-157E-4D67-91A0-CF52279CBF62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="624">
   <si>
     <t>2020-1</t>
   </si>
@@ -1594,6 +1594,318 @@
   </si>
   <si>
     <t xml:space="preserve"> 12/23/2024</t>
+  </si>
+  <si>
+    <t>2025-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/01/2025</t>
+  </si>
+  <si>
+    <t>2025-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/08/2025</t>
+  </si>
+  <si>
+    <t>2025-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/15/2025</t>
+  </si>
+  <si>
+    <t>2025-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/22/2025</t>
+  </si>
+  <si>
+    <t>2025-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/29/2025</t>
+  </si>
+  <si>
+    <t>2025-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02/05/2025</t>
+  </si>
+  <si>
+    <t>2025-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02/12/2025</t>
+  </si>
+  <si>
+    <t>2025-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02/19/2025</t>
+  </si>
+  <si>
+    <t>2025-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02/26/2025</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03/04/2025</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03/11/2025</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03/18/2025</t>
+  </si>
+  <si>
+    <t>2025-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03/25/2025</t>
+  </si>
+  <si>
+    <t>2025-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04/01/2025</t>
+  </si>
+  <si>
+    <t>2025-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04/08/2025</t>
+  </si>
+  <si>
+    <t>2025-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04/15/2025</t>
+  </si>
+  <si>
+    <t>2025-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04/22/2025</t>
+  </si>
+  <si>
+    <t>2025-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04/29/2025</t>
+  </si>
+  <si>
+    <t>2025-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 05/06/2025</t>
+  </si>
+  <si>
+    <t>2025-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 05/13/2025</t>
+  </si>
+  <si>
+    <t>2025-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 05/20/2025</t>
+  </si>
+  <si>
+    <t>2025-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 05/27/2025</t>
+  </si>
+  <si>
+    <t>2025-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 06/03/2025</t>
+  </si>
+  <si>
+    <t>2025-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 06/10/2025</t>
+  </si>
+  <si>
+    <t>2025-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 06/17/2025</t>
+  </si>
+  <si>
+    <t>2025-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 06/24/2025</t>
+  </si>
+  <si>
+    <t>2025-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07/01/2025</t>
+  </si>
+  <si>
+    <t>2025-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07/08/2025</t>
+  </si>
+  <si>
+    <t>2025-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07/15/2025</t>
+  </si>
+  <si>
+    <t>2025-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07/22/2025</t>
+  </si>
+  <si>
+    <t>2025-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07/29/2025</t>
+  </si>
+  <si>
+    <t>2025-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/05/2025</t>
+  </si>
+  <si>
+    <t>2025-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/12/2025</t>
+  </si>
+  <si>
+    <t>2025-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/19/2025</t>
+  </si>
+  <si>
+    <t>2025-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/26/2025</t>
+  </si>
+  <si>
+    <t>2025-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/02/2025</t>
+  </si>
+  <si>
+    <t>2025-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/09/2025</t>
+  </si>
+  <si>
+    <t>2025-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/16/2025</t>
+  </si>
+  <si>
+    <t>2025-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/23/2025</t>
+  </si>
+  <si>
+    <t>2025-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/30/2025</t>
+  </si>
+  <si>
+    <t>2025-41</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10/07/2025</t>
+  </si>
+  <si>
+    <t>2025-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10/14/2025</t>
+  </si>
+  <si>
+    <t>2025-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10/21/2025</t>
+  </si>
+  <si>
+    <t>2025-44</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10/28/2025</t>
+  </si>
+  <si>
+    <t>2025-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11/04/2025</t>
+  </si>
+  <si>
+    <t>2025-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11/11/2025</t>
+  </si>
+  <si>
+    <t>2025-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11/18/2025</t>
+  </si>
+  <si>
+    <t>2025-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11/25/2025</t>
+  </si>
+  <si>
+    <t>2025-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12/02/2025</t>
+  </si>
+  <si>
+    <t>2025-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12/09/2025</t>
+  </si>
+  <si>
+    <t>2025-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12/16/2025</t>
+  </si>
+  <si>
+    <t>2025-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12/23/2025</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D91FD6-4D52-4B60-BC4D-0EE8103371C9}">
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B312"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
@@ -4031,6 +4343,422 @@
         <v>519</v>
       </c>
     </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>520</v>
+      </c>
+      <c r="B261" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>524</v>
+      </c>
+      <c r="B263" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>526</v>
+      </c>
+      <c r="B264" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>530</v>
+      </c>
+      <c r="B266" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>532</v>
+      </c>
+      <c r="B267" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>534</v>
+      </c>
+      <c r="B268" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>536</v>
+      </c>
+      <c r="B269" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>538</v>
+      </c>
+      <c r="B270" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>540</v>
+      </c>
+      <c r="B271" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>542</v>
+      </c>
+      <c r="B272" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>544</v>
+      </c>
+      <c r="B273" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>546</v>
+      </c>
+      <c r="B274" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>548</v>
+      </c>
+      <c r="B275" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>550</v>
+      </c>
+      <c r="B276" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>552</v>
+      </c>
+      <c r="B277" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>554</v>
+      </c>
+      <c r="B278" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>556</v>
+      </c>
+      <c r="B279" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>558</v>
+      </c>
+      <c r="B280" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>560</v>
+      </c>
+      <c r="B281" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>562</v>
+      </c>
+      <c r="B282" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>564</v>
+      </c>
+      <c r="B283" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>566</v>
+      </c>
+      <c r="B284" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>568</v>
+      </c>
+      <c r="B285" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>570</v>
+      </c>
+      <c r="B286" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>572</v>
+      </c>
+      <c r="B287" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>574</v>
+      </c>
+      <c r="B288" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>576</v>
+      </c>
+      <c r="B289" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>578</v>
+      </c>
+      <c r="B290" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>580</v>
+      </c>
+      <c r="B291" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>582</v>
+      </c>
+      <c r="B292" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>584</v>
+      </c>
+      <c r="B293" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>586</v>
+      </c>
+      <c r="B294" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>588</v>
+      </c>
+      <c r="B295" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>590</v>
+      </c>
+      <c r="B296" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>592</v>
+      </c>
+      <c r="B297" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>594</v>
+      </c>
+      <c r="B298" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>596</v>
+      </c>
+      <c r="B299" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>598</v>
+      </c>
+      <c r="B300" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>600</v>
+      </c>
+      <c r="B301" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>602</v>
+      </c>
+      <c r="B302" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>604</v>
+      </c>
+      <c r="B303" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>606</v>
+      </c>
+      <c r="B304" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>608</v>
+      </c>
+      <c r="B305" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>610</v>
+      </c>
+      <c r="B306" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>612</v>
+      </c>
+      <c r="B307" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>614</v>
+      </c>
+      <c r="B308" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>616</v>
+      </c>
+      <c r="B309" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>618</v>
+      </c>
+      <c r="B310" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>620</v>
+      </c>
+      <c r="B311" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>622</v>
+      </c>
+      <c r="B312" t="s">
+        <v>623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
